--- a/etf_holdings/2026-08-28_00991A_full_holdings.xlsx
+++ b/etf_holdings/2026-08-28_00991A_full_holdings.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-28 06:14:05</t>
+          <t>2026-08-28 06:32:34</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -552,7 +552,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-08-28 06:14:05</t>
+          <t>2026-08-28 06:32:34</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -613,7 +613,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-08-28 06:14:05</t>
+          <t>2026-08-28 06:32:34</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -674,7 +674,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-08-28 06:14:05</t>
+          <t>2026-08-28 06:32:34</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -735,7 +735,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-08-28 06:14:05</t>
+          <t>2026-08-28 06:32:34</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-08-28 06:14:05</t>
+          <t>2026-08-28 06:32:34</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -857,7 +857,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-08-28 06:14:05</t>
+          <t>2026-08-28 06:32:34</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-08-28 06:14:05</t>
+          <t>2026-08-28 06:32:34</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-08-28 06:14:05</t>
+          <t>2026-08-28 06:32:34</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-08-28 06:14:05</t>
+          <t>2026-08-28 06:32:34</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-08-28 06:14:05</t>
+          <t>2026-08-28 06:32:34</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-08-28 06:14:05</t>
+          <t>2026-08-28 06:32:34</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-08-28 06:14:05</t>
+          <t>2026-08-28 06:32:34</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1284,7 +1284,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-08-28 06:14:05</t>
+          <t>2026-08-28 06:32:34</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1345,7 +1345,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-08-28 06:14:05</t>
+          <t>2026-08-28 06:32:34</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-08-28 06:14:07</t>
+          <t>2026-08-28 06:32:35</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1467,7 +1467,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-08-28 06:14:07</t>
+          <t>2026-08-28 06:32:35</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-08-28 06:14:07</t>
+          <t>2026-08-28 06:32:35</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1589,7 +1589,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-08-28 06:14:07</t>
+          <t>2026-08-28 06:32:35</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1650,7 +1650,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-08-28 06:14:07</t>
+          <t>2026-08-28 06:32:35</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-08-28 06:14:07</t>
+          <t>2026-08-28 06:32:35</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1772,7 +1772,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-08-28 06:14:07</t>
+          <t>2026-08-28 06:32:35</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1833,7 +1833,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-08-28 06:14:07</t>
+          <t>2026-08-28 06:32:35</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-08-28 06:14:07</t>
+          <t>2026-08-28 06:32:35</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-08-28 06:14:07</t>
+          <t>2026-08-28 06:32:35</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-08-28 06:14:07</t>
+          <t>2026-08-28 06:32:35</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2077,7 +2077,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-08-28 06:14:07</t>
+          <t>2026-08-28 06:32:35</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2138,7 +2138,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-08-28 06:14:07</t>
+          <t>2026-08-28 06:32:35</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2199,7 +2199,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-08-28 06:14:07</t>
+          <t>2026-08-28 06:32:35</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2260,7 +2260,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-08-28 06:14:07</t>
+          <t>2026-08-28 06:32:35</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2321,7 +2321,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-08-28 06:14:08</t>
+          <t>2026-08-28 06:32:37</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-08-28 06:14:08</t>
+          <t>2026-08-28 06:32:37</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2443,7 +2443,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-08-28 06:14:08</t>
+          <t>2026-08-28 06:32:37</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2504,7 +2504,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-08-28 06:14:08</t>
+          <t>2026-08-28 06:32:37</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2565,7 +2565,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-08-28 06:14:08</t>
+          <t>2026-08-28 06:32:37</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2626,7 +2626,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-08-28 06:14:08</t>
+          <t>2026-08-28 06:32:37</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2687,7 +2687,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-08-28 06:14:08</t>
+          <t>2026-08-28 06:32:37</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2748,7 +2748,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-08-28 06:14:08</t>
+          <t>2026-08-28 06:32:37</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2809,7 +2809,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-08-28 06:14:08</t>
+          <t>2026-08-28 06:32:37</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2870,7 +2870,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-08-28 06:14:08</t>
+          <t>2026-08-28 06:32:37</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2931,7 +2931,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-08-28 06:14:08</t>
+          <t>2026-08-28 06:32:37</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -2992,7 +2992,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-08-28 06:14:08</t>
+          <t>2026-08-28 06:32:37</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3053,7 +3053,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-08-28 06:14:08</t>
+          <t>2026-08-28 06:32:37</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3114,7 +3114,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-08-28 06:14:08</t>
+          <t>2026-08-28 06:32:37</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3175,7 +3175,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-08-28 06:14:08</t>
+          <t>2026-08-28 06:32:37</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -3236,7 +3236,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2026-08-28 06:14:09</t>
+          <t>2026-08-28 06:32:38</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -3297,7 +3297,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-08-28 06:14:09</t>
+          <t>2026-08-28 06:32:38</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -3358,7 +3358,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-08-28 06:14:09</t>
+          <t>2026-08-28 06:32:38</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -3419,7 +3419,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2026-08-28 06:14:09</t>
+          <t>2026-08-28 06:32:38</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -3480,7 +3480,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2026-08-28 06:14:09</t>
+          <t>2026-08-28 06:32:38</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">

--- a/etf_holdings/2026-08-28_00991A_full_holdings.xlsx
+++ b/etf_holdings/2026-08-28_00991A_full_holdings.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-28 06:32:34</t>
+          <t>2026-08-28 06:58:09</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -552,7 +552,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-08-28 06:32:34</t>
+          <t>2026-08-28 06:58:09</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -613,7 +613,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-08-28 06:32:34</t>
+          <t>2026-08-28 06:58:09</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -674,7 +674,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-08-28 06:32:34</t>
+          <t>2026-08-28 06:58:09</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -735,7 +735,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-08-28 06:32:34</t>
+          <t>2026-08-28 06:58:09</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-08-28 06:32:34</t>
+          <t>2026-08-28 06:58:09</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -857,7 +857,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-08-28 06:32:34</t>
+          <t>2026-08-28 06:58:09</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-08-28 06:32:34</t>
+          <t>2026-08-28 06:58:09</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-08-28 06:32:34</t>
+          <t>2026-08-28 06:58:09</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-08-28 06:32:34</t>
+          <t>2026-08-28 06:58:09</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-08-28 06:32:34</t>
+          <t>2026-08-28 06:58:09</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-08-28 06:32:34</t>
+          <t>2026-08-28 06:58:09</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-08-28 06:32:34</t>
+          <t>2026-08-28 06:58:09</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1284,7 +1284,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-08-28 06:32:34</t>
+          <t>2026-08-28 06:58:09</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1345,7 +1345,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-08-28 06:32:34</t>
+          <t>2026-08-28 06:58:09</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-08-28 06:32:35</t>
+          <t>2026-08-28 06:58:10</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1467,7 +1467,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-08-28 06:32:35</t>
+          <t>2026-08-28 06:58:10</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-08-28 06:32:35</t>
+          <t>2026-08-28 06:58:10</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1589,7 +1589,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-08-28 06:32:35</t>
+          <t>2026-08-28 06:58:10</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1650,7 +1650,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-08-28 06:32:35</t>
+          <t>2026-08-28 06:58:10</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-08-28 06:32:35</t>
+          <t>2026-08-28 06:58:10</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1772,7 +1772,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-08-28 06:32:35</t>
+          <t>2026-08-28 06:58:10</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1833,7 +1833,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-08-28 06:32:35</t>
+          <t>2026-08-28 06:58:10</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-08-28 06:32:35</t>
+          <t>2026-08-28 06:58:10</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-08-28 06:32:35</t>
+          <t>2026-08-28 06:58:10</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-08-28 06:32:35</t>
+          <t>2026-08-28 06:58:10</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2077,7 +2077,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-08-28 06:32:35</t>
+          <t>2026-08-28 06:58:10</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2138,7 +2138,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-08-28 06:32:35</t>
+          <t>2026-08-28 06:58:10</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2199,7 +2199,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-08-28 06:32:35</t>
+          <t>2026-08-28 06:58:10</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2260,7 +2260,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-08-28 06:32:35</t>
+          <t>2026-08-28 06:58:10</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2321,7 +2321,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-08-28 06:32:37</t>
+          <t>2026-08-28 06:58:12</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-08-28 06:32:37</t>
+          <t>2026-08-28 06:58:12</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2443,7 +2443,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-08-28 06:32:37</t>
+          <t>2026-08-28 06:58:12</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2504,7 +2504,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-08-28 06:32:37</t>
+          <t>2026-08-28 06:58:12</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2565,7 +2565,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-08-28 06:32:37</t>
+          <t>2026-08-28 06:58:12</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2626,7 +2626,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-08-28 06:32:37</t>
+          <t>2026-08-28 06:58:12</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2687,7 +2687,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-08-28 06:32:37</t>
+          <t>2026-08-28 06:58:12</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2748,7 +2748,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-08-28 06:32:37</t>
+          <t>2026-08-28 06:58:12</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2809,7 +2809,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-08-28 06:32:37</t>
+          <t>2026-08-28 06:58:12</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2870,7 +2870,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-08-28 06:32:37</t>
+          <t>2026-08-28 06:58:12</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2931,7 +2931,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-08-28 06:32:37</t>
+          <t>2026-08-28 06:58:12</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -2992,7 +2992,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-08-28 06:32:37</t>
+          <t>2026-08-28 06:58:12</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3053,7 +3053,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-08-28 06:32:37</t>
+          <t>2026-08-28 06:58:12</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3114,7 +3114,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-08-28 06:32:37</t>
+          <t>2026-08-28 06:58:12</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3175,7 +3175,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-08-28 06:32:37</t>
+          <t>2026-08-28 06:58:12</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -3236,7 +3236,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2026-08-28 06:32:38</t>
+          <t>2026-08-28 06:58:13</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -3297,7 +3297,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-08-28 06:32:38</t>
+          <t>2026-08-28 06:58:13</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -3358,7 +3358,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-08-28 06:32:38</t>
+          <t>2026-08-28 06:58:13</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -3419,7 +3419,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2026-08-28 06:32:38</t>
+          <t>2026-08-28 06:58:13</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -3480,7 +3480,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2026-08-28 06:32:38</t>
+          <t>2026-08-28 06:58:13</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">

--- a/etf_holdings/2026-08-28_00991A_full_holdings.xlsx
+++ b/etf_holdings/2026-08-28_00991A_full_holdings.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-28 06:58:09</t>
+          <t>2026-08-28 15:43:27</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -509,16 +509,16 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>-0.21%2410</t>
+          <t>+0.41%2420</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>-0.21%</t>
+          <t>+0.41%</t>
         </is>
       </c>
       <c r="H2" t="n">
-        <v>2410</v>
+        <v>2420</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
@@ -535,7 +535,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>-0.02%</t>
+          <t>+0.05%</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -552,7 +552,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-08-28 06:58:09</t>
+          <t>2026-08-28 15:43:27</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -570,16 +570,16 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>-6.7%5500</t>
+          <t>0%5490</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>-6.7%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="H3" t="n">
-        <v>5500</v>
+        <v>5490</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -596,7 +596,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>-0.65%</t>
+          <t>+0.00%</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -613,7 +613,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-08-28 06:58:09</t>
+          <t>2026-08-28 15:43:27</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -631,16 +631,16 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>+4.64%541</t>
+          <t>-0.18%540</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>+4.64%</t>
+          <t>-0.18%</t>
         </is>
       </c>
       <c r="H4" t="n">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
@@ -657,7 +657,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>+0.39%</t>
+          <t>-0.02%</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -674,7 +674,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-08-28 06:58:09</t>
+          <t>2026-08-28 15:43:27</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -692,16 +692,16 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>0%14340</t>
+          <t>-0.28%14300</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>-0.28%</t>
         </is>
       </c>
       <c r="H5" t="n">
-        <v>14340</v>
+        <v>14300</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -718,7 +718,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>-0.02%</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -735,7 +735,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-08-28 06:58:09</t>
+          <t>2026-08-28 15:43:27</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -753,16 +753,16 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>+1.72%1180</t>
+          <t>-5.93%1110</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>+1.72%</t>
+          <t>-5.93%</t>
         </is>
       </c>
       <c r="H6" t="n">
-        <v>1180</v>
+        <v>1110</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
@@ -779,7 +779,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>+0.12%</t>
+          <t>-0.43%</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-08-28 06:58:09</t>
+          <t>2026-08-28 15:43:27</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -814,16 +814,16 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>+3.35%555</t>
+          <t>+7.57%597</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>+3.35%</t>
+          <t>+7.57%</t>
         </is>
       </c>
       <c r="H7" t="n">
-        <v>555</v>
+        <v>597</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
@@ -840,7 +840,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>+0.16%</t>
+          <t>+0.35%</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -857,7 +857,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-08-28 06:58:09</t>
+          <t>2026-08-28 15:43:27</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -875,16 +875,16 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>+9.75%1295</t>
+          <t>-4.25%1240</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>+9.75%</t>
+          <t>-4.25%</t>
         </is>
       </c>
       <c r="H8" t="n">
-        <v>1295</v>
+        <v>1240</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
@@ -901,7 +901,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>+0.44%</t>
+          <t>-0.22%</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-08-28 06:58:09</t>
+          <t>2026-08-28 15:43:27</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -936,16 +936,16 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>+5.86%3340</t>
+          <t>+0.6%3360</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>+5.86%</t>
+          <t>+0.6%</t>
         </is>
       </c>
       <c r="H9" t="n">
-        <v>3340</v>
+        <v>3360</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
@@ -962,7 +962,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>+0.27%</t>
+          <t>+0.03%</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-08-28 06:58:09</t>
+          <t>2026-08-28 15:43:27</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -997,16 +997,16 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>+0.44%6815</t>
+          <t>+5.65%7200</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>+0.44%</t>
+          <t>+5.65%</t>
         </is>
       </c>
       <c r="H10" t="n">
-        <v>6815</v>
+        <v>7200</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
@@ -1023,7 +1023,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>+0.02%</t>
+          <t>+0.26%</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-08-28 06:58:09</t>
+          <t>2026-08-28 15:43:27</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1058,16 +1058,16 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>-2.03%3865</t>
+          <t>+3.1%3985</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>-2.03%</t>
+          <t>+3.1%</t>
         </is>
       </c>
       <c r="H11" t="n">
-        <v>3865</v>
+        <v>3985</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>-0.09%</t>
+          <t>+0.14%</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-08-28 06:58:09</t>
+          <t>2026-08-28 15:43:27</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1119,16 +1119,16 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>+3.75%914</t>
+          <t>-1.64%899</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>+3.75%</t>
+          <t>-1.64%</t>
         </is>
       </c>
       <c r="H12" t="n">
-        <v>914</v>
+        <v>899</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
@@ -1145,7 +1145,7 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>+0.16%</t>
+          <t>-0.07%</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-08-28 06:58:09</t>
+          <t>2026-08-28 15:43:27</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1180,16 +1180,16 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>+1.7%2090</t>
+          <t>+1.67%2125</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>+1.7%</t>
+          <t>+1.67%</t>
         </is>
       </c>
       <c r="H13" t="n">
-        <v>2090</v>
+        <v>2125</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
@@ -1223,7 +1223,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-08-28 06:58:09</t>
+          <t>2026-08-28 15:43:27</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1241,16 +1241,16 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>-5.56%1445</t>
+          <t>+3.11%1490</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>-5.56%</t>
+          <t>+3.11%</t>
         </is>
       </c>
       <c r="H14" t="n">
-        <v>1445</v>
+        <v>1490</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
@@ -1267,7 +1267,7 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>-0.24%</t>
+          <t>+0.12%</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
@@ -1284,7 +1284,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-08-28 06:58:09</t>
+          <t>2026-08-28 15:43:27</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1302,16 +1302,16 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>+3.53%3370</t>
+          <t>-1.93%3305</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>+3.53%</t>
+          <t>-1.93%</t>
         </is>
       </c>
       <c r="H15" t="n">
-        <v>3370</v>
+        <v>3305</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
@@ -1328,7 +1328,7 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>+0.11%</t>
+          <t>-0.06%</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
@@ -1345,7 +1345,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-08-28 06:58:09</t>
+          <t>2026-08-28 15:43:27</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1363,16 +1363,16 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>+0.99%5090</t>
+          <t>-1.18%5030</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>+0.99%</t>
+          <t>-1.18%</t>
         </is>
       </c>
       <c r="H16" t="n">
-        <v>5090</v>
+        <v>5030</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
@@ -1389,7 +1389,7 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>+0.03%</t>
+          <t>-0.03%</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-08-28 06:58:10</t>
+          <t>2026-08-28 15:43:28</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1424,16 +1424,16 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>+0.16%6345</t>
+          <t>+2.29%6490</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>+0.16%</t>
+          <t>+2.29%</t>
         </is>
       </c>
       <c r="H17" t="n">
-        <v>6345</v>
+        <v>6490</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
@@ -1450,7 +1450,7 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>+0.06%</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
@@ -1467,7 +1467,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-08-28 06:58:10</t>
+          <t>2026-08-28 15:43:28</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1485,16 +1485,16 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>-1.4%5645</t>
+          <t>+2.48%5785</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>-1.4%</t>
+          <t>+2.48%</t>
         </is>
       </c>
       <c r="H18" t="n">
-        <v>5645</v>
+        <v>5785</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
@@ -1511,7 +1511,7 @@
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>-0.03%</t>
+          <t>+0.05%</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-08-28 06:58:10</t>
+          <t>2026-08-28 15:43:28</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1546,16 +1546,16 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>+1.41%2155</t>
+          <t>-0.23%2150</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>+1.41%</t>
+          <t>-0.23%</t>
         </is>
       </c>
       <c r="H19" t="n">
-        <v>2155</v>
+        <v>2150</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
@@ -1572,7 +1572,7 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>+0.03%</t>
+          <t>-0.01%</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
@@ -1589,7 +1589,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-08-28 06:58:10</t>
+          <t>2026-08-28 15:43:28</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1607,16 +1607,16 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>-2.45%15305</t>
+          <t>+2.12%15630</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>-2.45%</t>
+          <t>+2.12%</t>
         </is>
       </c>
       <c r="H20" t="n">
-        <v>15305</v>
+        <v>15630</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
@@ -1633,7 +1633,7 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>-0.05%</t>
+          <t>+0.04%</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
@@ -1650,7 +1650,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-08-28 06:58:10</t>
+          <t>2026-08-28 15:43:28</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1668,7 +1668,7 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>+9.93%675</t>
+          <t>+9.93%742</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -1677,7 +1677,7 @@
         </is>
       </c>
       <c r="H21" t="n">
-        <v>675</v>
+        <v>742</v>
       </c>
       <c r="I21" t="inlineStr">
         <is>
@@ -1711,7 +1711,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-08-28 06:58:10</t>
+          <t>2026-08-28 15:43:28</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1729,16 +1729,16 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>+9.94%6915</t>
+          <t>+2.17%7065</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>+9.94%</t>
+          <t>+2.17%</t>
         </is>
       </c>
       <c r="H22" t="n">
-        <v>6915</v>
+        <v>7065</v>
       </c>
       <c r="I22" t="inlineStr">
         <is>
@@ -1772,7 +1772,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-08-28 06:58:10</t>
+          <t>2026-08-28 15:43:28</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1790,16 +1790,16 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>+2.2%605</t>
+          <t>+2.64%621</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>+2.2%</t>
+          <t>+2.64%</t>
         </is>
       </c>
       <c r="H23" t="n">
-        <v>605</v>
+        <v>621</v>
       </c>
       <c r="I23" t="inlineStr">
         <is>
@@ -1833,7 +1833,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-08-28 06:58:10</t>
+          <t>2026-08-28 15:43:28</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1851,16 +1851,16 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>+0.3%333.5</t>
+          <t>-0.3%332.5</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>+0.3%</t>
+          <t>-0.3%</t>
         </is>
       </c>
       <c r="H24" t="n">
-        <v>333.5</v>
+        <v>332.5</v>
       </c>
       <c r="I24" t="inlineStr">
         <is>
@@ -1877,7 +1877,7 @@
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>-0.00%</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-08-28 06:58:10</t>
+          <t>2026-08-28 15:43:28</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1912,16 +1912,16 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>+2.23%252</t>
+          <t>+0.4%253</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>+2.23%</t>
+          <t>+0.4%</t>
         </is>
       </c>
       <c r="H25" t="n">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="I25" t="inlineStr">
         <is>
@@ -1955,7 +1955,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-08-28 06:58:10</t>
+          <t>2026-08-28 15:43:28</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -1973,16 +1973,16 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>+0.65%232.5</t>
+          <t>-0.43%231.5</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>+0.65%</t>
+          <t>-0.43%</t>
         </is>
       </c>
       <c r="H26" t="n">
-        <v>232.5</v>
+        <v>231.5</v>
       </c>
       <c r="I26" t="inlineStr">
         <is>
@@ -1999,7 +1999,7 @@
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>-0.00%</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-08-28 06:58:10</t>
+          <t>2026-08-28 15:43:28</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2034,16 +2034,16 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>+0.51%1990</t>
+          <t>+1.01%2010</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>+0.51%</t>
+          <t>+1.01%</t>
         </is>
       </c>
       <c r="H27" t="n">
-        <v>1990</v>
+        <v>2010</v>
       </c>
       <c r="I27" t="inlineStr">
         <is>
@@ -2077,7 +2077,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-08-28 06:58:10</t>
+          <t>2026-08-28 15:43:28</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2095,16 +2095,16 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>+2.49%2055</t>
+          <t>+9.98%2260</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>+2.49%</t>
+          <t>+9.98%</t>
         </is>
       </c>
       <c r="H28" t="n">
-        <v>2055</v>
+        <v>2260</v>
       </c>
       <c r="I28" t="inlineStr">
         <is>
@@ -2138,7 +2138,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-08-28 06:58:10</t>
+          <t>2026-08-28 15:43:28</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2156,16 +2156,16 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>+1.14%1770</t>
+          <t>+3.39%1830</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>+1.14%</t>
+          <t>+3.39%</t>
         </is>
       </c>
       <c r="H29" t="n">
-        <v>1770</v>
+        <v>1830</v>
       </c>
       <c r="I29" t="inlineStr">
         <is>
@@ -2199,7 +2199,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-08-28 06:58:10</t>
+          <t>2026-08-28 15:43:28</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2217,16 +2217,16 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>-1.37%179.5</t>
+          <t>-0.84%178</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>-1.37%</t>
+          <t>-0.84%</t>
         </is>
       </c>
       <c r="H30" t="n">
-        <v>179.5</v>
+        <v>178</v>
       </c>
       <c r="I30" t="inlineStr">
         <is>
@@ -2260,7 +2260,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-08-28 06:58:10</t>
+          <t>2026-08-28 15:43:28</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2278,16 +2278,16 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>-0.66%151</t>
+          <t>+1.32%153</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>-0.66%</t>
+          <t>+1.32%</t>
         </is>
       </c>
       <c r="H31" t="n">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="I31" t="inlineStr">
         <is>
@@ -2304,7 +2304,7 @@
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>-0.00%</t>
+          <t>+0.00%</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
@@ -2321,7 +2321,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-08-28 06:58:12</t>
+          <t>2026-08-28 15:43:29</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2339,16 +2339,16 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>+2.17%141.5</t>
+          <t>+1.77%144</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>+2.17%</t>
+          <t>+1.77%</t>
         </is>
       </c>
       <c r="H32" t="n">
-        <v>141.5</v>
+        <v>144</v>
       </c>
       <c r="I32" t="inlineStr">
         <is>
@@ -2382,7 +2382,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-08-28 06:58:12</t>
+          <t>2026-08-28 15:43:29</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2400,12 +2400,12 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>-0.46%1075</t>
+          <t>0%1075</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>-0.46%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="H33" t="n">
@@ -2426,7 +2426,7 @@
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>-0.00%</t>
+          <t>+0.00%</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
@@ -2443,7 +2443,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-08-28 06:58:12</t>
+          <t>2026-08-28 15:43:29</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2461,7 +2461,7 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>-0.31%968</t>
+          <t>-0.31%965</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
@@ -2470,7 +2470,7 @@
         </is>
       </c>
       <c r="H34" t="n">
-        <v>968</v>
+        <v>965</v>
       </c>
       <c r="I34" t="inlineStr">
         <is>
@@ -2504,7 +2504,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-08-28 06:58:12</t>
+          <t>2026-08-28 15:43:29</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2522,16 +2522,16 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>0%102.5</t>
+          <t>+2.93%105.5</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>+2.93%</t>
         </is>
       </c>
       <c r="H35" t="n">
-        <v>102.5</v>
+        <v>105.5</v>
       </c>
       <c r="I35" t="inlineStr">
         <is>
@@ -2565,7 +2565,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-08-28 06:58:12</t>
+          <t>2026-08-28 15:43:29</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2583,16 +2583,16 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>-0.54%730</t>
+          <t>-1.1%722</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>-0.54%</t>
+          <t>-1.1%</t>
         </is>
       </c>
       <c r="H36" t="n">
-        <v>730</v>
+        <v>722</v>
       </c>
       <c r="I36" t="inlineStr">
         <is>
@@ -2626,7 +2626,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-08-28 06:58:12</t>
+          <t>2026-08-28 15:43:29</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2644,16 +2644,16 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>+0.64%63.2</t>
+          <t>+1.27%64</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>+0.64%</t>
+          <t>+1.27%</t>
         </is>
       </c>
       <c r="H37" t="n">
-        <v>63.2</v>
+        <v>64</v>
       </c>
       <c r="I37" t="inlineStr">
         <is>
@@ -2687,7 +2687,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-08-28 06:58:12</t>
+          <t>2026-08-28 15:43:29</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2705,16 +2705,16 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>-1.24%63.8</t>
+          <t>+0.94%64.4</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>-1.24%</t>
+          <t>+0.94%</t>
         </is>
       </c>
       <c r="H38" t="n">
-        <v>63.8</v>
+        <v>64.40000000000001</v>
       </c>
       <c r="I38" t="inlineStr">
         <is>
@@ -2731,7 +2731,7 @@
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>-0.00%</t>
+          <t>+0.00%</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
@@ -2748,7 +2748,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-08-28 06:58:12</t>
+          <t>2026-08-28 15:43:29</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2766,16 +2766,16 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>0%481</t>
+          <t>+1.87%490</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>+1.87%</t>
         </is>
       </c>
       <c r="H39" t="n">
-        <v>481</v>
+        <v>490</v>
       </c>
       <c r="I39" t="inlineStr">
         <is>
@@ -2809,7 +2809,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-08-28 06:58:12</t>
+          <t>2026-08-28 15:43:29</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2827,16 +2827,16 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>+0.51%39.35</t>
+          <t>+1.14%39.8</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>+0.51%</t>
+          <t>+1.14%</t>
         </is>
       </c>
       <c r="H40" t="n">
-        <v>39.35</v>
+        <v>39.8</v>
       </c>
       <c r="I40" t="inlineStr">
         <is>
@@ -2870,7 +2870,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-08-28 06:58:12</t>
+          <t>2026-08-28 15:43:29</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2888,16 +2888,16 @@
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>-0.97%46.15</t>
+          <t>+4.44%48.2</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>-0.97%</t>
+          <t>+4.44%</t>
         </is>
       </c>
       <c r="H41" t="n">
-        <v>46.15</v>
+        <v>48.2</v>
       </c>
       <c r="I41" t="inlineStr">
         <is>
@@ -2931,7 +2931,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-08-28 06:58:12</t>
+          <t>2026-08-28 15:43:29</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -2949,16 +2949,16 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>+1.43%247.5</t>
+          <t>+9.09%270</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>+1.43%</t>
+          <t>+9.09%</t>
         </is>
       </c>
       <c r="H42" t="n">
-        <v>247.5</v>
+        <v>270</v>
       </c>
       <c r="I42" t="inlineStr">
         <is>
@@ -2992,7 +2992,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-08-28 06:58:12</t>
+          <t>2026-08-28 15:43:29</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3010,16 +3010,16 @@
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>-0.39%38.55</t>
+          <t>+0.52%38.75</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>-0.39%</t>
+          <t>+0.52%</t>
         </is>
       </c>
       <c r="H43" t="n">
-        <v>38.55</v>
+        <v>38.75</v>
       </c>
       <c r="I43" t="inlineStr">
         <is>
@@ -3053,7 +3053,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-08-28 06:58:12</t>
+          <t>2026-08-28 15:43:29</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3071,16 +3071,16 @@
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>-0.63%39.35</t>
+          <t>+2.29%40.25</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>-0.63%</t>
+          <t>+2.29%</t>
         </is>
       </c>
       <c r="H44" t="n">
-        <v>39.35</v>
+        <v>40.25</v>
       </c>
       <c r="I44" t="inlineStr">
         <is>
@@ -3114,7 +3114,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-08-28 06:58:12</t>
+          <t>2026-08-28 15:43:29</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3132,16 +3132,16 @@
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>-0.31%32.15</t>
+          <t>+1.87%32.75</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>-0.31%</t>
+          <t>+1.87%</t>
         </is>
       </c>
       <c r="H45" t="n">
-        <v>32.15</v>
+        <v>32.75</v>
       </c>
       <c r="I45" t="inlineStr">
         <is>
@@ -3175,7 +3175,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-08-28 06:58:12</t>
+          <t>2026-08-28 15:43:29</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -3193,16 +3193,16 @@
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>-0.53%37.3</t>
+          <t>+0.54%37.5</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>-0.53%</t>
+          <t>+0.54%</t>
         </is>
       </c>
       <c r="H46" t="n">
-        <v>37.3</v>
+        <v>37.5</v>
       </c>
       <c r="I46" t="inlineStr">
         <is>
@@ -3236,7 +3236,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2026-08-28 06:58:13</t>
+          <t>2026-08-28 15:43:31</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -3254,16 +3254,16 @@
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>+9.91%244</t>
+          <t>-1.23%241</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>+9.91%</t>
+          <t>-1.23%</t>
         </is>
       </c>
       <c r="H47" t="n">
-        <v>244</v>
+        <v>241</v>
       </c>
       <c r="I47" t="inlineStr">
         <is>
@@ -3297,7 +3297,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-08-28 06:58:13</t>
+          <t>2026-08-28 15:43:31</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -3315,16 +3315,16 @@
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>-1.12%220.5</t>
+          <t>-0.91%218.5</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>-1.12%</t>
+          <t>-0.91%</t>
         </is>
       </c>
       <c r="H48" t="n">
-        <v>220.5</v>
+        <v>218.5</v>
       </c>
       <c r="I48" t="inlineStr">
         <is>
@@ -3358,7 +3358,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-08-28 06:58:13</t>
+          <t>2026-08-28 15:43:31</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -3376,16 +3376,16 @@
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>-1.78%193</t>
+          <t>+1.55%196</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>-1.78%</t>
+          <t>+1.55%</t>
         </is>
       </c>
       <c r="H49" t="n">
-        <v>193</v>
+        <v>196</v>
       </c>
       <c r="I49" t="inlineStr">
         <is>
@@ -3419,7 +3419,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2026-08-28 06:58:13</t>
+          <t>2026-08-28 15:43:31</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -3437,12 +3437,12 @@
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>-0.37%135.5</t>
+          <t>0%135.5</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>-0.37%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="H50" t="n">
@@ -3480,7 +3480,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2026-08-28 06:58:13</t>
+          <t>2026-08-28 15:43:31</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -3498,16 +3498,16 @@
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>-0.77%77.1</t>
+          <t>-1.82%75.7</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>-0.77%</t>
+          <t>-1.82%</t>
         </is>
       </c>
       <c r="H51" t="n">
-        <v>77.09999999999999</v>
+        <v>75.7</v>
       </c>
       <c r="I51" t="inlineStr">
         <is>

--- a/etf_holdings/2026-08-28_00991A_full_holdings.xlsx
+++ b/etf_holdings/2026-08-28_00991A_full_holdings.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-28 15:43:27</t>
+          <t>2026-08-28 17:23:49</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -522,16 +522,16 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>11.74%4,200,000</t>
+          <t>11.30%4,000,000</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>11.74%</t>
+          <t>11.30%</t>
         </is>
       </c>
       <c r="K2" t="n">
-        <v>4200000</v>
+        <v>4000000</v>
       </c>
       <c r="L2" t="inlineStr">
         <is>
@@ -552,7 +552,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-08-28 15:43:27</t>
+          <t>2026-08-28 17:23:49</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -583,12 +583,12 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>8.93%1,400,000</t>
+          <t>8.97%1,400,000</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>8.93%</t>
+          <t>8.97%</t>
         </is>
       </c>
       <c r="K3" t="n">
@@ -613,7 +613,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-08-28 15:43:27</t>
+          <t>2026-08-28 17:23:49</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -644,12 +644,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>8.78%14,000,000</t>
+          <t>8.82%14,000,000</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>8.78%</t>
+          <t>8.82%</t>
         </is>
       </c>
       <c r="K4" t="n">
@@ -674,7 +674,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-08-28 15:43:27</t>
+          <t>2026-08-28 17:23:49</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -705,12 +705,12 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>8.48%510,000</t>
+          <t>8.51%510,000</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>8.48%</t>
+          <t>8.51%</t>
         </is>
       </c>
       <c r="K5" t="n">
@@ -735,7 +735,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-08-28 15:43:27</t>
+          <t>2026-08-28 17:23:49</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -766,12 +766,12 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>6.84%5,000,000</t>
+          <t>6.48%5,000,000</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>6.84%</t>
+          <t>6.48%</t>
         </is>
       </c>
       <c r="K6" t="n">
@@ -779,7 +779,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>-0.43%</t>
+          <t>-0.41%</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-08-28 15:43:27</t>
+          <t>2026-08-28 17:23:49</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -827,12 +827,12 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>4.96%7,700,000</t>
+          <t>5.37%7,700,000</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>4.96%</t>
+          <t>5.37%</t>
         </is>
       </c>
       <c r="K7" t="n">
@@ -840,7 +840,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>+0.35%</t>
+          <t>+0.38%</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -857,7 +857,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-08-28 15:43:27</t>
+          <t>2026-08-28 17:23:49</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -870,38 +870,38 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>8046南亞電路</t>
+          <t>6669緯穎科技</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>-4.25%1240</t>
+          <t>+5.65%7200</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>-4.25%</t>
+          <t>+5.65%</t>
         </is>
       </c>
       <c r="H8" t="n">
-        <v>1240</v>
+        <v>7200</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>4.88%3,250,000</t>
+          <t>5.04%600,000</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>4.88%</t>
+          <t>5.04%</t>
         </is>
       </c>
       <c r="K8" t="n">
-        <v>3250000</v>
+        <v>600000</v>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>-0.22%</t>
+          <t>+0.27%</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-08-28 15:43:27</t>
+          <t>2026-08-28 17:23:49</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -949,12 +949,12 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>4.84%1,250,000</t>
+          <t>4.90%1,250,000</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>4.84%</t>
+          <t>4.90%</t>
         </is>
       </c>
       <c r="K9" t="n">
@@ -979,7 +979,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-08-28 15:43:27</t>
+          <t>2026-08-28 17:23:49</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -992,38 +992,38 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>6669緯穎科技</t>
+          <t>8046南亞電路</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>+5.65%7200</t>
+          <t>-4.25%1240</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>+5.65%</t>
+          <t>-4.25%</t>
         </is>
       </c>
       <c r="H10" t="n">
-        <v>7200</v>
+        <v>1240</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>4.74%600,000</t>
+          <t>4.70%3,250,000</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>4.74%</t>
+          <t>4.70%</t>
         </is>
       </c>
       <c r="K10" t="n">
-        <v>600000</v>
+        <v>3250000</v>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>+0.26%</t>
+          <t>-0.21%</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-08-28 15:43:27</t>
+          <t>2026-08-28 17:23:49</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1071,12 +1071,12 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>4.48%1,000,000</t>
+          <t>4.65%1,000,000</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>4.48%</t>
+          <t>4.65%</t>
         </is>
       </c>
       <c r="K11" t="n">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-08-28 15:43:27</t>
+          <t>2026-08-28 17:23:49</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1132,12 +1132,12 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>4.34%4,100,000</t>
+          <t>4.30%4,100,000</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>4.34%</t>
+          <t>4.30%</t>
         </is>
       </c>
       <c r="K12" t="n">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-08-28 15:43:27</t>
+          <t>2026-08-28 17:23:49</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1193,12 +1193,12 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>4.12%1,700,000</t>
+          <t>4.22%1,700,000</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>4.12%</t>
+          <t>4.22%</t>
         </is>
       </c>
       <c r="K13" t="n">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-08-28 15:43:27</t>
+          <t>2026-08-28 17:23:49</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1254,12 +1254,12 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>4.02%2,400,000</t>
+          <t>4.17%2,400,000</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>4.02%</t>
+          <t>4.17%</t>
         </is>
       </c>
       <c r="K14" t="n">
@@ -1267,7 +1267,7 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>+0.12%</t>
+          <t>+0.13%</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
@@ -1284,7 +1284,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-08-28 15:43:27</t>
+          <t>2026-08-28 17:23:49</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1315,12 +1315,12 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>3.13%800,000</t>
+          <t>3.09%800,000</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>3.13%</t>
+          <t>3.09%</t>
         </is>
       </c>
       <c r="K15" t="n">
@@ -1345,7 +1345,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-08-28 15:43:27</t>
+          <t>2026-08-28 17:23:49</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1358,38 +1358,38 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>6223旺矽科技</t>
+          <t>7769鴻勁精密</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>-1.18%5030</t>
+          <t>+2.29%6490</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>-1.18%</t>
+          <t>+2.29%</t>
         </is>
       </c>
       <c r="H16" t="n">
-        <v>5030</v>
+        <v>6490</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>2.71%460,000</t>
+          <t>2.73%360,000</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>2.71%</t>
+          <t>2.73%</t>
         </is>
       </c>
       <c r="K16" t="n">
-        <v>460000</v>
+        <v>360000</v>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>-0.03%</t>
+          <t>+0.06%</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-08-28 15:43:28</t>
+          <t>2026-08-28 17:23:50</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1419,38 +1419,38 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>7769鴻勁精密</t>
+          <t>3026禾伸堂企</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>+2.29%6490</t>
+          <t>+9.93%742</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>+2.29%</t>
+          <t>+9.93%</t>
         </is>
       </c>
       <c r="H17" t="n">
-        <v>6490</v>
+        <v>742</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>2.65%360,000</t>
+          <t>2.34%2,700,000</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>2.65%</t>
+          <t>2.34%</t>
         </is>
       </c>
       <c r="K17" t="n">
-        <v>360000</v>
+        <v>2700000</v>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>+0.06%</t>
+          <t>+0.21%</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
@@ -1467,7 +1467,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-08-28 15:43:28</t>
+          <t>2026-08-28 17:23:50</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1498,12 +1498,12 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>2.23%340,000</t>
+          <t>2.30%340,000</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>2.23%</t>
+          <t>2.30%</t>
         </is>
       </c>
       <c r="K18" t="n">
@@ -1511,7 +1511,7 @@
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>+0.05%</t>
+          <t>+0.06%</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-08-28 15:43:28</t>
+          <t>2026-08-28 17:23:50</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1541,38 +1541,38 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>8299群聯電子</t>
+          <t>6223旺矽科技</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>-0.23%2150</t>
+          <t>-1.18%5030</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>-0.23%</t>
+          <t>-1.18%</t>
         </is>
       </c>
       <c r="H19" t="n">
-        <v>2150</v>
+        <v>5030</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>2.20%880,000</t>
+          <t>2.23%380,000</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>2.20%</t>
+          <t>2.23%</t>
         </is>
       </c>
       <c r="K19" t="n">
-        <v>880000</v>
+        <v>380000</v>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>-0.01%</t>
+          <t>-0.03%</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
@@ -1589,7 +1589,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-08-28 15:43:28</t>
+          <t>2026-08-28 17:23:50</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1602,38 +1602,38 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>5274信驊科技</t>
+          <t>8299群聯電子</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>+2.12%15630</t>
+          <t>-0.23%2150</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>+2.12%</t>
+          <t>-0.23%</t>
         </is>
       </c>
       <c r="H20" t="n">
-        <v>15630</v>
+        <v>2150</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>2.14%120,500</t>
+          <t>2.21%880,000</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>2.14%</t>
+          <t>2.21%</t>
         </is>
       </c>
       <c r="K20" t="n">
-        <v>120500</v>
+        <v>880000</v>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>+0.04%</t>
+          <t>-0.01%</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
@@ -1650,7 +1650,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-08-28 15:43:28</t>
+          <t>2026-08-28 17:23:50</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1663,38 +1663,38 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>3026禾伸堂企</t>
+          <t>5274信驊科技</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>+9.93%742</t>
+          <t>+2.12%15630</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>+9.93%</t>
+          <t>+2.12%</t>
         </is>
       </c>
       <c r="H21" t="n">
-        <v>742</v>
+        <v>15630</v>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>2.11%2,700,000</t>
+          <t>2.20%120,500</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>2.11%</t>
+          <t>2.20%</t>
         </is>
       </c>
       <c r="K21" t="n">
-        <v>2700000</v>
+        <v>120500</v>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>+0.19%</t>
+          <t>+0.05%</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-08-28 15:43:28</t>
+          <t>2026-08-28 17:23:50</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1772,7 +1772,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-08-28 15:43:28</t>
+          <t>2026-08-28 17:23:50</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1833,7 +1833,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-08-28 15:43:28</t>
+          <t>2026-08-28 17:23:50</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-08-28 15:43:28</t>
+          <t>2026-08-28 17:23:50</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-08-28 15:43:28</t>
+          <t>2026-08-28 17:23:50</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -1968,25 +1968,25 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>2603長榮海運</t>
+          <t>3665貿聯-KY</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>-0.43%231.5</t>
+          <t>+9.98%2260</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>-0.43%</t>
+          <t>+9.98%</t>
         </is>
       </c>
       <c r="H26" t="n">
-        <v>231.5</v>
+        <v>2260</v>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>&lt;0.01%9,000</t>
+          <t>&lt;0.01%1,000</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
@@ -1995,11 +1995,11 @@
         </is>
       </c>
       <c r="K26" t="n">
-        <v>9000</v>
+        <v>1000</v>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>-0.00%</t>
+          <t>+0.00%</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-08-28 15:43:28</t>
+          <t>2026-08-28 17:23:50</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2029,25 +2029,25 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>2360致茂電子</t>
+          <t>2603長榮海運</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>+1.01%2010</t>
+          <t>-0.43%231.5</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>+1.01%</t>
+          <t>-0.43%</t>
         </is>
       </c>
       <c r="H27" t="n">
-        <v>2010</v>
+        <v>231.5</v>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>&lt;0.01%1,000</t>
+          <t>&lt;0.01%9,000</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
@@ -2056,11 +2056,11 @@
         </is>
       </c>
       <c r="K27" t="n">
-        <v>1000</v>
+        <v>9000</v>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>-0.00%</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
@@ -2077,7 +2077,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-08-28 15:43:28</t>
+          <t>2026-08-28 17:23:50</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2090,21 +2090,21 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>3665貿聯-KY</t>
+          <t>2360致茂電子</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>+9.98%2260</t>
+          <t>+1.01%2010</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>+9.98%</t>
+          <t>+1.01%</t>
         </is>
       </c>
       <c r="H28" t="n">
-        <v>2260</v>
+        <v>2010</v>
       </c>
       <c r="I28" t="inlineStr">
         <is>
@@ -2138,7 +2138,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-08-28 15:43:28</t>
+          <t>2026-08-28 17:23:50</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2199,7 +2199,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-08-28 15:43:28</t>
+          <t>2026-08-28 17:23:50</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2260,7 +2260,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-08-28 15:43:28</t>
+          <t>2026-08-28 17:23:50</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2321,7 +2321,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-08-28 15:43:29</t>
+          <t>2026-08-28 17:23:52</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-08-28 15:43:29</t>
+          <t>2026-08-28 17:23:52</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2443,7 +2443,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-08-28 15:43:29</t>
+          <t>2026-08-28 17:23:52</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2504,7 +2504,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-08-28 15:43:29</t>
+          <t>2026-08-28 17:23:52</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2565,7 +2565,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-08-28 15:43:29</t>
+          <t>2026-08-28 17:23:52</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2626,7 +2626,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-08-28 15:43:29</t>
+          <t>2026-08-28 17:23:52</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2687,7 +2687,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-08-28 15:43:29</t>
+          <t>2026-08-28 17:23:52</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2748,7 +2748,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-08-28 15:43:29</t>
+          <t>2026-08-28 17:23:52</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2809,7 +2809,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-08-28 15:43:29</t>
+          <t>2026-08-28 17:23:52</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2822,30 +2822,30 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>2890永豐金融</t>
+          <t>2886兆豐金融</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>+1.14%39.8</t>
+          <t>+4.44%48.2</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>+1.14%</t>
+          <t>+4.44%</t>
         </is>
       </c>
       <c r="H40" t="n">
-        <v>39.8</v>
+        <v>48.2</v>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>0%9,000</t>
+          <t>&lt;0.01%9,000</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>&lt;0.01%</t>
         </is>
       </c>
       <c r="K40" t="n">
@@ -2870,7 +2870,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-08-28 15:43:29</t>
+          <t>2026-08-28 17:23:52</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2883,25 +2883,25 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>2886兆豐金融</t>
+          <t>2449京元電子</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>+4.44%48.2</t>
+          <t>+9.09%270</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>+4.44%</t>
+          <t>+9.09%</t>
         </is>
       </c>
       <c r="H41" t="n">
-        <v>48.2</v>
+        <v>270</v>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>0%9,000</t>
+          <t>0%1,450</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
@@ -2910,7 +2910,7 @@
         </is>
       </c>
       <c r="K41" t="n">
-        <v>9000</v>
+        <v>1450</v>
       </c>
       <c r="L41" t="inlineStr">
         <is>
@@ -2931,7 +2931,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-08-28 15:43:29</t>
+          <t>2026-08-28 17:23:52</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -2944,25 +2944,25 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>2449京元電子</t>
+          <t>2884玉山金融</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>+9.09%270</t>
+          <t>+0.52%38.75</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>+9.09%</t>
+          <t>+0.52%</t>
         </is>
       </c>
       <c r="H42" t="n">
-        <v>270</v>
+        <v>38.75</v>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>0%1,450</t>
+          <t>0%9,000</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
@@ -2971,7 +2971,7 @@
         </is>
       </c>
       <c r="K42" t="n">
-        <v>1450</v>
+        <v>9000</v>
       </c>
       <c r="L42" t="inlineStr">
         <is>
@@ -2992,7 +2992,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-08-28 15:43:29</t>
+          <t>2026-08-28 17:23:52</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3005,25 +3005,25 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>2884玉山金融</t>
+          <t>2880華南金融</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>+0.52%38.75</t>
+          <t>+2.29%40.25</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>+0.52%</t>
+          <t>+2.29%</t>
         </is>
       </c>
       <c r="H43" t="n">
-        <v>38.75</v>
+        <v>40.25</v>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>0%9,000</t>
+          <t>0%9,090</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
@@ -3032,7 +3032,7 @@
         </is>
       </c>
       <c r="K43" t="n">
-        <v>9000</v>
+        <v>9090</v>
       </c>
       <c r="L43" t="inlineStr">
         <is>
@@ -3053,7 +3053,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-08-28 15:43:29</t>
+          <t>2026-08-28 17:23:52</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3066,25 +3066,25 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>2880華南金融</t>
+          <t>2890永豐金融</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>+2.29%40.25</t>
+          <t>+1.14%39.8</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>+2.29%</t>
+          <t>+1.14%</t>
         </is>
       </c>
       <c r="H44" t="n">
-        <v>40.25</v>
+        <v>39.8</v>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>0%9,090</t>
+          <t>0%9,000</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
@@ -3093,7 +3093,7 @@
         </is>
       </c>
       <c r="K44" t="n">
-        <v>9090</v>
+        <v>9000</v>
       </c>
       <c r="L44" t="inlineStr">
         <is>
@@ -3114,7 +3114,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-08-28 15:43:29</t>
+          <t>2026-08-28 17:23:52</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3175,7 +3175,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-08-28 15:43:29</t>
+          <t>2026-08-28 17:23:52</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -3236,7 +3236,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2026-08-28 15:43:31</t>
+          <t>2026-08-28 17:23:53</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -3297,7 +3297,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-08-28 15:43:31</t>
+          <t>2026-08-28 17:23:53</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -3358,7 +3358,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-08-28 15:43:31</t>
+          <t>2026-08-28 17:23:53</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -3419,7 +3419,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2026-08-28 15:43:31</t>
+          <t>2026-08-28 17:23:53</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -3480,7 +3480,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2026-08-28 15:43:31</t>
+          <t>2026-08-28 17:23:53</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">

--- a/etf_holdings/2026-08-28_00991A_full_holdings.xlsx
+++ b/etf_holdings/2026-08-28_00991A_full_holdings.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-28 17:23:49</t>
+          <t>2026-08-28 19:06:10</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -552,7 +552,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-08-28 17:23:49</t>
+          <t>2026-08-28 19:06:10</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -613,7 +613,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-08-28 17:23:49</t>
+          <t>2026-08-28 19:06:10</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -674,7 +674,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-08-28 17:23:49</t>
+          <t>2026-08-28 19:06:10</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -735,7 +735,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-08-28 17:23:49</t>
+          <t>2026-08-28 19:06:10</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-08-28 17:23:49</t>
+          <t>2026-08-28 19:06:10</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -857,7 +857,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-08-28 17:23:49</t>
+          <t>2026-08-28 19:06:10</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-08-28 17:23:49</t>
+          <t>2026-08-28 19:06:10</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-08-28 17:23:49</t>
+          <t>2026-08-28 19:06:10</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-08-28 17:23:49</t>
+          <t>2026-08-28 19:06:10</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-08-28 17:23:49</t>
+          <t>2026-08-28 19:06:10</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-08-28 17:23:49</t>
+          <t>2026-08-28 19:06:10</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-08-28 17:23:49</t>
+          <t>2026-08-28 19:06:10</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1284,7 +1284,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-08-28 17:23:49</t>
+          <t>2026-08-28 19:06:10</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1345,7 +1345,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-08-28 17:23:49</t>
+          <t>2026-08-28 19:06:10</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-08-28 17:23:50</t>
+          <t>2026-08-28 19:06:11</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1467,7 +1467,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-08-28 17:23:50</t>
+          <t>2026-08-28 19:06:11</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-08-28 17:23:50</t>
+          <t>2026-08-28 19:06:11</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1589,7 +1589,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-08-28 17:23:50</t>
+          <t>2026-08-28 19:06:11</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1650,7 +1650,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-08-28 17:23:50</t>
+          <t>2026-08-28 19:06:11</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-08-28 17:23:50</t>
+          <t>2026-08-28 19:06:11</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1772,7 +1772,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-08-28 17:23:50</t>
+          <t>2026-08-28 19:06:11</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1833,7 +1833,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-08-28 17:23:50</t>
+          <t>2026-08-28 19:06:11</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-08-28 17:23:50</t>
+          <t>2026-08-28 19:06:11</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-08-28 17:23:50</t>
+          <t>2026-08-28 19:06:11</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-08-28 17:23:50</t>
+          <t>2026-08-28 19:06:11</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2077,7 +2077,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-08-28 17:23:50</t>
+          <t>2026-08-28 19:06:11</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2138,7 +2138,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-08-28 17:23:50</t>
+          <t>2026-08-28 19:06:11</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2199,7 +2199,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-08-28 17:23:50</t>
+          <t>2026-08-28 19:06:11</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2260,7 +2260,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-08-28 17:23:50</t>
+          <t>2026-08-28 19:06:11</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2321,7 +2321,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-08-28 17:23:52</t>
+          <t>2026-08-28 19:06:13</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-08-28 17:23:52</t>
+          <t>2026-08-28 19:06:13</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2443,7 +2443,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-08-28 17:23:52</t>
+          <t>2026-08-28 19:06:13</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2504,7 +2504,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-08-28 17:23:52</t>
+          <t>2026-08-28 19:06:13</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2565,7 +2565,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-08-28 17:23:52</t>
+          <t>2026-08-28 19:06:13</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2626,7 +2626,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-08-28 17:23:52</t>
+          <t>2026-08-28 19:06:13</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2687,7 +2687,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-08-28 17:23:52</t>
+          <t>2026-08-28 19:06:13</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2748,7 +2748,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-08-28 17:23:52</t>
+          <t>2026-08-28 19:06:13</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2809,7 +2809,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-08-28 17:23:52</t>
+          <t>2026-08-28 19:06:13</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2870,7 +2870,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-08-28 17:23:52</t>
+          <t>2026-08-28 19:06:13</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2931,7 +2931,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-08-28 17:23:52</t>
+          <t>2026-08-28 19:06:13</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -2992,7 +2992,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-08-28 17:23:52</t>
+          <t>2026-08-28 19:06:13</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3053,7 +3053,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-08-28 17:23:52</t>
+          <t>2026-08-28 19:06:13</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3114,7 +3114,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-08-28 17:23:52</t>
+          <t>2026-08-28 19:06:13</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3175,7 +3175,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-08-28 17:23:52</t>
+          <t>2026-08-28 19:06:13</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -3236,7 +3236,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2026-08-28 17:23:53</t>
+          <t>2026-08-28 19:06:14</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -3297,7 +3297,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-08-28 17:23:53</t>
+          <t>2026-08-28 19:06:14</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -3358,7 +3358,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-08-28 17:23:53</t>
+          <t>2026-08-28 19:06:14</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -3419,7 +3419,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2026-08-28 17:23:53</t>
+          <t>2026-08-28 19:06:14</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -3480,7 +3480,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2026-08-28 17:23:53</t>
+          <t>2026-08-28 19:06:14</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">

--- a/etf_holdings/2026-08-28_00991A_full_holdings.xlsx
+++ b/etf_holdings/2026-08-28_00991A_full_holdings.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-28 19:06:10</t>
+          <t>2026-08-28 20:37:50</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -552,7 +552,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-08-28 19:06:10</t>
+          <t>2026-08-28 20:37:50</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -613,7 +613,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-08-28 19:06:10</t>
+          <t>2026-08-28 20:37:50</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -674,7 +674,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-08-28 19:06:10</t>
+          <t>2026-08-28 20:37:50</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -735,7 +735,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-08-28 19:06:10</t>
+          <t>2026-08-28 20:37:50</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-08-28 19:06:10</t>
+          <t>2026-08-28 20:37:50</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -857,7 +857,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-08-28 19:06:10</t>
+          <t>2026-08-28 20:37:50</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-08-28 19:06:10</t>
+          <t>2026-08-28 20:37:50</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-08-28 19:06:10</t>
+          <t>2026-08-28 20:37:50</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-08-28 19:06:10</t>
+          <t>2026-08-28 20:37:50</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-08-28 19:06:10</t>
+          <t>2026-08-28 20:37:50</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-08-28 19:06:10</t>
+          <t>2026-08-28 20:37:50</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-08-28 19:06:10</t>
+          <t>2026-08-28 20:37:50</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1284,7 +1284,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-08-28 19:06:10</t>
+          <t>2026-08-28 20:37:50</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1345,7 +1345,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-08-28 19:06:10</t>
+          <t>2026-08-28 20:37:50</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-08-28 19:06:11</t>
+          <t>2026-08-28 20:37:52</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1467,7 +1467,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-08-28 19:06:11</t>
+          <t>2026-08-28 20:37:52</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-08-28 19:06:11</t>
+          <t>2026-08-28 20:37:52</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1589,7 +1589,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-08-28 19:06:11</t>
+          <t>2026-08-28 20:37:52</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1650,7 +1650,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-08-28 19:06:11</t>
+          <t>2026-08-28 20:37:52</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-08-28 19:06:11</t>
+          <t>2026-08-28 20:37:52</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1772,7 +1772,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-08-28 19:06:11</t>
+          <t>2026-08-28 20:37:52</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1833,7 +1833,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-08-28 19:06:11</t>
+          <t>2026-08-28 20:37:52</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-08-28 19:06:11</t>
+          <t>2026-08-28 20:37:52</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-08-28 19:06:11</t>
+          <t>2026-08-28 20:37:52</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-08-28 19:06:11</t>
+          <t>2026-08-28 20:37:52</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2077,7 +2077,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-08-28 19:06:11</t>
+          <t>2026-08-28 20:37:52</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2138,7 +2138,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-08-28 19:06:11</t>
+          <t>2026-08-28 20:37:52</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2199,7 +2199,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-08-28 19:06:11</t>
+          <t>2026-08-28 20:37:52</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2260,7 +2260,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-08-28 19:06:11</t>
+          <t>2026-08-28 20:37:52</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2321,7 +2321,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-08-28 19:06:13</t>
+          <t>2026-08-28 20:37:53</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-08-28 19:06:13</t>
+          <t>2026-08-28 20:37:53</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2443,7 +2443,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-08-28 19:06:13</t>
+          <t>2026-08-28 20:37:53</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2504,7 +2504,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-08-28 19:06:13</t>
+          <t>2026-08-28 20:37:53</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2565,7 +2565,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-08-28 19:06:13</t>
+          <t>2026-08-28 20:37:53</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2626,7 +2626,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-08-28 19:06:13</t>
+          <t>2026-08-28 20:37:53</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2687,7 +2687,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-08-28 19:06:13</t>
+          <t>2026-08-28 20:37:53</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2748,7 +2748,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-08-28 19:06:13</t>
+          <t>2026-08-28 20:37:53</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2809,7 +2809,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-08-28 19:06:13</t>
+          <t>2026-08-28 20:37:53</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2870,7 +2870,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-08-28 19:06:13</t>
+          <t>2026-08-28 20:37:53</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2931,7 +2931,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-08-28 19:06:13</t>
+          <t>2026-08-28 20:37:53</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -2992,7 +2992,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-08-28 19:06:13</t>
+          <t>2026-08-28 20:37:53</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3053,7 +3053,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-08-28 19:06:13</t>
+          <t>2026-08-28 20:37:53</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3114,7 +3114,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-08-28 19:06:13</t>
+          <t>2026-08-28 20:37:53</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3175,7 +3175,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-08-28 19:06:13</t>
+          <t>2026-08-28 20:37:53</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -3236,7 +3236,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2026-08-28 19:06:14</t>
+          <t>2026-08-28 20:37:54</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -3297,7 +3297,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-08-28 19:06:14</t>
+          <t>2026-08-28 20:37:54</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -3358,7 +3358,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-08-28 19:06:14</t>
+          <t>2026-08-28 20:37:54</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -3419,7 +3419,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2026-08-28 19:06:14</t>
+          <t>2026-08-28 20:37:54</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -3480,7 +3480,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2026-08-28 19:06:14</t>
+          <t>2026-08-28 20:37:54</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">

--- a/etf_holdings/2026-08-28_00991A_full_holdings.xlsx
+++ b/etf_holdings/2026-08-28_00991A_full_holdings.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-28 20:37:50</t>
+          <t>2026-08-28 21:39:53</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -552,7 +552,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-08-28 20:37:50</t>
+          <t>2026-08-28 21:39:53</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -613,7 +613,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-08-28 20:37:50</t>
+          <t>2026-08-28 21:39:53</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -674,7 +674,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-08-28 20:37:50</t>
+          <t>2026-08-28 21:39:53</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -735,7 +735,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-08-28 20:37:50</t>
+          <t>2026-08-28 21:39:53</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-08-28 20:37:50</t>
+          <t>2026-08-28 21:39:53</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -857,7 +857,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-08-28 20:37:50</t>
+          <t>2026-08-28 21:39:53</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-08-28 20:37:50</t>
+          <t>2026-08-28 21:39:53</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-08-28 20:37:50</t>
+          <t>2026-08-28 21:39:53</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-08-28 20:37:50</t>
+          <t>2026-08-28 21:39:53</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-08-28 20:37:50</t>
+          <t>2026-08-28 21:39:53</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-08-28 20:37:50</t>
+          <t>2026-08-28 21:39:53</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-08-28 20:37:50</t>
+          <t>2026-08-28 21:39:53</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1284,7 +1284,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-08-28 20:37:50</t>
+          <t>2026-08-28 21:39:53</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1345,7 +1345,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-08-28 20:37:50</t>
+          <t>2026-08-28 21:39:53</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-08-28 20:37:52</t>
+          <t>2026-08-28 21:39:54</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1467,7 +1467,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-08-28 20:37:52</t>
+          <t>2026-08-28 21:39:54</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-08-28 20:37:52</t>
+          <t>2026-08-28 21:39:54</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1589,7 +1589,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-08-28 20:37:52</t>
+          <t>2026-08-28 21:39:54</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1650,7 +1650,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-08-28 20:37:52</t>
+          <t>2026-08-28 21:39:54</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-08-28 20:37:52</t>
+          <t>2026-08-28 21:39:54</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1772,7 +1772,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-08-28 20:37:52</t>
+          <t>2026-08-28 21:39:54</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1833,7 +1833,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-08-28 20:37:52</t>
+          <t>2026-08-28 21:39:54</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-08-28 20:37:52</t>
+          <t>2026-08-28 21:39:54</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-08-28 20:37:52</t>
+          <t>2026-08-28 21:39:54</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-08-28 20:37:52</t>
+          <t>2026-08-28 21:39:54</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2077,7 +2077,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-08-28 20:37:52</t>
+          <t>2026-08-28 21:39:54</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2138,7 +2138,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-08-28 20:37:52</t>
+          <t>2026-08-28 21:39:54</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2199,7 +2199,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-08-28 20:37:52</t>
+          <t>2026-08-28 21:39:54</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2260,7 +2260,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-08-28 20:37:52</t>
+          <t>2026-08-28 21:39:54</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2321,7 +2321,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-08-28 20:37:53</t>
+          <t>2026-08-28 21:39:55</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-08-28 20:37:53</t>
+          <t>2026-08-28 21:39:55</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2443,7 +2443,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-08-28 20:37:53</t>
+          <t>2026-08-28 21:39:55</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2504,7 +2504,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-08-28 20:37:53</t>
+          <t>2026-08-28 21:39:55</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2565,7 +2565,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-08-28 20:37:53</t>
+          <t>2026-08-28 21:39:55</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2626,7 +2626,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-08-28 20:37:53</t>
+          <t>2026-08-28 21:39:55</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2687,7 +2687,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-08-28 20:37:53</t>
+          <t>2026-08-28 21:39:55</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2748,7 +2748,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-08-28 20:37:53</t>
+          <t>2026-08-28 21:39:55</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2809,7 +2809,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-08-28 20:37:53</t>
+          <t>2026-08-28 21:39:55</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2870,7 +2870,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-08-28 20:37:53</t>
+          <t>2026-08-28 21:39:55</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2931,7 +2931,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-08-28 20:37:53</t>
+          <t>2026-08-28 21:39:55</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -2992,7 +2992,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-08-28 20:37:53</t>
+          <t>2026-08-28 21:39:55</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3053,7 +3053,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-08-28 20:37:53</t>
+          <t>2026-08-28 21:39:55</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3114,7 +3114,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-08-28 20:37:53</t>
+          <t>2026-08-28 21:39:55</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3175,7 +3175,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-08-28 20:37:53</t>
+          <t>2026-08-28 21:39:55</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -3236,7 +3236,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2026-08-28 20:37:54</t>
+          <t>2026-08-28 21:39:57</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -3297,7 +3297,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-08-28 20:37:54</t>
+          <t>2026-08-28 21:39:57</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -3358,7 +3358,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-08-28 20:37:54</t>
+          <t>2026-08-28 21:39:57</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -3419,7 +3419,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2026-08-28 20:37:54</t>
+          <t>2026-08-28 21:39:57</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -3480,7 +3480,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2026-08-28 20:37:54</t>
+          <t>2026-08-28 21:39:57</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">

--- a/etf_holdings/2026-08-28_00991A_full_holdings.xlsx
+++ b/etf_holdings/2026-08-28_00991A_full_holdings.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-28 21:39:53</t>
+          <t>2026-08-28 21:45:59</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -552,7 +552,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-08-28 21:39:53</t>
+          <t>2026-08-28 21:45:59</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -613,7 +613,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-08-28 21:39:53</t>
+          <t>2026-08-28 21:45:59</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -674,7 +674,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-08-28 21:39:53</t>
+          <t>2026-08-28 21:45:59</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -735,7 +735,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-08-28 21:39:53</t>
+          <t>2026-08-28 21:45:59</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-08-28 21:39:53</t>
+          <t>2026-08-28 21:45:59</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -857,7 +857,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-08-28 21:39:53</t>
+          <t>2026-08-28 21:45:59</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-08-28 21:39:53</t>
+          <t>2026-08-28 21:45:59</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-08-28 21:39:53</t>
+          <t>2026-08-28 21:45:59</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-08-28 21:39:53</t>
+          <t>2026-08-28 21:45:59</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-08-28 21:39:53</t>
+          <t>2026-08-28 21:45:59</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-08-28 21:39:53</t>
+          <t>2026-08-28 21:45:59</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-08-28 21:39:53</t>
+          <t>2026-08-28 21:45:59</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1284,7 +1284,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-08-28 21:39:53</t>
+          <t>2026-08-28 21:45:59</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1345,7 +1345,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-08-28 21:39:53</t>
+          <t>2026-08-28 21:45:59</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-08-28 21:39:54</t>
+          <t>2026-08-28 21:46:01</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1467,7 +1467,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-08-28 21:39:54</t>
+          <t>2026-08-28 21:46:01</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-08-28 21:39:54</t>
+          <t>2026-08-28 21:46:01</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1589,7 +1589,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-08-28 21:39:54</t>
+          <t>2026-08-28 21:46:01</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1650,7 +1650,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-08-28 21:39:54</t>
+          <t>2026-08-28 21:46:01</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-08-28 21:39:54</t>
+          <t>2026-08-28 21:46:01</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1772,7 +1772,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-08-28 21:39:54</t>
+          <t>2026-08-28 21:46:01</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1833,7 +1833,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-08-28 21:39:54</t>
+          <t>2026-08-28 21:46:01</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-08-28 21:39:54</t>
+          <t>2026-08-28 21:46:01</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-08-28 21:39:54</t>
+          <t>2026-08-28 21:46:01</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-08-28 21:39:54</t>
+          <t>2026-08-28 21:46:01</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2077,7 +2077,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-08-28 21:39:54</t>
+          <t>2026-08-28 21:46:01</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2138,7 +2138,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-08-28 21:39:54</t>
+          <t>2026-08-28 21:46:01</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2199,7 +2199,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-08-28 21:39:54</t>
+          <t>2026-08-28 21:46:01</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2260,7 +2260,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-08-28 21:39:54</t>
+          <t>2026-08-28 21:46:01</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2321,7 +2321,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-08-28 21:39:55</t>
+          <t>2026-08-28 21:46:02</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-08-28 21:39:55</t>
+          <t>2026-08-28 21:46:02</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2443,7 +2443,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-08-28 21:39:55</t>
+          <t>2026-08-28 21:46:02</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2504,7 +2504,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-08-28 21:39:55</t>
+          <t>2026-08-28 21:46:02</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2565,7 +2565,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-08-28 21:39:55</t>
+          <t>2026-08-28 21:46:02</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2626,7 +2626,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-08-28 21:39:55</t>
+          <t>2026-08-28 21:46:02</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2687,7 +2687,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-08-28 21:39:55</t>
+          <t>2026-08-28 21:46:02</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2748,7 +2748,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-08-28 21:39:55</t>
+          <t>2026-08-28 21:46:02</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2809,7 +2809,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-08-28 21:39:55</t>
+          <t>2026-08-28 21:46:02</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2870,7 +2870,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-08-28 21:39:55</t>
+          <t>2026-08-28 21:46:02</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2931,7 +2931,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-08-28 21:39:55</t>
+          <t>2026-08-28 21:46:02</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -2992,7 +2992,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-08-28 21:39:55</t>
+          <t>2026-08-28 21:46:02</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3053,7 +3053,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-08-28 21:39:55</t>
+          <t>2026-08-28 21:46:02</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3114,7 +3114,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-08-28 21:39:55</t>
+          <t>2026-08-28 21:46:02</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3175,7 +3175,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-08-28 21:39:55</t>
+          <t>2026-08-28 21:46:02</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -3236,7 +3236,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2026-08-28 21:39:57</t>
+          <t>2026-08-28 21:46:03</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -3297,7 +3297,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-08-28 21:39:57</t>
+          <t>2026-08-28 21:46:03</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -3358,7 +3358,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-08-28 21:39:57</t>
+          <t>2026-08-28 21:46:03</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -3419,7 +3419,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2026-08-28 21:39:57</t>
+          <t>2026-08-28 21:46:03</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -3480,7 +3480,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2026-08-28 21:39:57</t>
+          <t>2026-08-28 21:46:03</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
